--- a/GLOVETESTER-NFCBOARD/Project Outputs for GLOVETESTER-NFCBOARD/BOM/Bill of Materials-GLOVETESTER-NFCBOARD(Manufacturing).xlsx
+++ b/GLOVETESTER-NFCBOARD/Project Outputs for GLOVETESTER-NFCBOARD/BOM/Bill of Materials-GLOVETESTER-NFCBOARD(Manufacturing).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silardgal\Documents\Development\PROSYS-GLOVETESTER-NFCBOARD\GLOVETESTER-NFCBOARD\Project Outputs for GLOVETESTER-NFCBOARD\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CC574B-CE52-44BC-A81B-C77259116B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD153EDD-44B1-4D9C-9B7D-99D29F6CC5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7E5D142D-EC5C-4CDC-A49C-0FB3AED26FBF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{52330587-C68C-4C1A-81D5-77B8DEC84B04}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-GLOVETESTER-N" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
   <si>
     <t>MPN</t>
   </si>
@@ -45,6 +45,18 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>DFE252012F-4R7M=P2</t>
+  </si>
+  <si>
+    <t>4.7uH 1.5A</t>
+  </si>
+  <si>
+    <t>4.7 µH Shielded Drum Core, Wirewound Inductor 1.5 A 190mOhm Max 1008 (2520 Metric) Flat Wire</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
     <t>ABM3B-27.120MHZ-10-D1G-T</t>
   </si>
   <si>
@@ -57,31 +69,13 @@
     <t>Y1</t>
   </si>
   <si>
-    <t>560085-0101 (Loose Piece)</t>
-  </si>
-  <si>
-    <t>Headers &amp; Wire Housings Crimp Term Rec Fem 22-26AWG Loose Pc</t>
-  </si>
-  <si>
-    <t>J1, J2, J3, J4, J5, J6, J7, J8, J9, J10</t>
-  </si>
-  <si>
-    <t>502352-1000</t>
-  </si>
-  <si>
-    <t>Headers &amp; Wire Housings WTB Header SR RA 11 Crcts Tin Plating NAT</t>
-  </si>
-  <si>
-    <t>J11</t>
-  </si>
-  <si>
-    <t>502351-1000</t>
-  </si>
-  <si>
-    <t>Headers &amp; Wire Housings WTB Recp Housing SR 12 Crcts NAT</t>
-  </si>
-  <si>
-    <t>J12</t>
+    <t>1770940</t>
+  </si>
+  <si>
+    <t>Fixed Terminal Blocks PTSM 0,5/ 8-2,5-H THR R32</t>
+  </si>
+  <si>
+    <t>J1</t>
   </si>
   <si>
     <t>GCM155R71H104KE02D</t>
@@ -93,7 +87,7 @@
     <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 0.1 uF 50 VDC 10% 0402 X7R AEC-Q200</t>
   </si>
   <si>
-    <t>C2, C21</t>
+    <t>C2, C21, C24</t>
   </si>
   <si>
     <t>GRM155R61H105KE05D</t>
@@ -105,7 +99,7 @@
     <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 1 uF 50 VDC 10% 0402 X5R</t>
   </si>
   <si>
-    <t>C4</t>
+    <t>C4, C25</t>
   </si>
   <si>
     <t>GRT188R61H225KE13D</t>
@@ -144,6 +138,18 @@
     <t>C5, C12</t>
   </si>
   <si>
+    <t>GCM31CR71A226KE02L</t>
+  </si>
+  <si>
+    <t>22u 10V</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 22 uF 10 VDC 10% 1206 X7R AEC-Q200</t>
+  </si>
+  <si>
+    <t>C26, C27</t>
+  </si>
+  <si>
     <t>GCM1555C2A680JE02D</t>
   </si>
   <si>
@@ -201,6 +207,21 @@
     <t>L1, L2</t>
   </si>
   <si>
+    <t>AP63203WU-7</t>
+  </si>
+  <si>
+    <t>Switching Voltage Regulators DCDC Conv HV Buck TSOT26 T&amp;R 3K 3V3 OUT</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>Test Point 1mm</t>
+  </si>
+  <si>
+    <t>TP1, TP2, TP3, TP4, TP5, TP6, TP7</t>
+  </si>
+  <si>
     <t>RC0402FR-070RL</t>
   </si>
   <si>
@@ -210,7 +231,7 @@
     <t>Thick Film Resistors - SMD General Purpose Chip Resistor 0402, 0Ohms, 1%, 1/16W</t>
   </si>
   <si>
-    <t>R1, R3, R4, R5, R6, R11, R12, R13, R14, R16, R17, R18, R26</t>
+    <t>R1, R18</t>
   </si>
   <si>
     <t>RC0402JR-7D2K2L</t>
@@ -246,7 +267,7 @@
     <t>Thick Film Resistors - SMD General Purpose Chip Resistor 0402, 10kOhms, 1%, 1/16W</t>
   </si>
   <si>
-    <t>R20, R22, R25</t>
+    <t>R25</t>
   </si>
 </sst>
 </file>
@@ -622,15 +643,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CEDE68D-F3CB-46FD-AC88-113E72F60965}">
-  <dimension ref="A1:E19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C540568C-3E01-4290-9362-2D598848B095}">
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="68.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" customWidth="1"/>
-    <col min="5" max="5" width="46.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -672,30 +693,30 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -703,33 +724,33 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -737,50 +758,50 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -788,16 +809,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -805,16 +826,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
@@ -822,16 +843,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -839,16 +860,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -856,16 +877,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -873,16 +894,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
@@ -890,50 +911,48 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="E17" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -941,19 +960,53 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="1">
-        <v>3</v>
+      <c r="B20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
